--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -528,7 +528,7 @@
         <v>1618</v>
       </c>
       <c r="M2" t="n">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="N2" t="n">
         <v>3</v>
@@ -574,7 +574,7 @@
         <v>201</v>
       </c>
       <c r="M3" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -620,7 +620,7 @@
         <v>784</v>
       </c>
       <c r="M4" t="n">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="N4" t="n">
         <v>5</v>
@@ -666,10 +666,10 @@
         <v>319</v>
       </c>
       <c r="M5" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -896,10 +896,10 @@
         <v>613</v>
       </c>
       <c r="M10" t="n">
-        <v>598</v>
+        <v>672</v>
       </c>
       <c r="N10" t="n">
-        <v>18</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -899,7 +899,7 @@
         <v>672</v>
       </c>
       <c r="N10" t="n">
-        <v>80</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -623,7 +623,7 @@
         <v>525</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -669,7 +669,7 @@
         <v>161</v>
       </c>
       <c r="N5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
@@ -899,7 +899,7 @@
         <v>672</v>
       </c>
       <c r="N10" t="n">
-        <v>112</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -899,7 +899,7 @@
         <v>672</v>
       </c>
       <c r="N10" t="n">
-        <v>180</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -531,7 +531,7 @@
         <v>887</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -623,7 +623,7 @@
         <v>525</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -669,7 +669,7 @@
         <v>161</v>
       </c>
       <c r="N5" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
@@ -761,7 +761,7 @@
         <v>27</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -807,7 +807,7 @@
         <v>10</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -899,7 +899,7 @@
         <v>672</v>
       </c>
       <c r="N10" t="n">
-        <v>205</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -1,40 +1,120 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>GMV slab</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>£0-£50</t>
+  </si>
+  <si>
+    <t>£50-£100</t>
+  </si>
+  <si>
+    <t>£100-£1K</t>
+  </si>
+  <si>
+    <t>£1K-£5K</t>
+  </si>
+  <si>
+    <t>£5K-£10K</t>
+  </si>
+  <si>
+    <t>£10K-£25K</t>
+  </si>
+  <si>
+    <t>£25K-£50K</t>
+  </si>
+  <si>
+    <t>£50K+</t>
+  </si>
+  <si>
+    <t>No data</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +122,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,501 +439,451 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>GMV slab</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="n">
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>12</v>
+      </c>
+      <c r="C2">
         <v>247</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>406</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>508</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>311</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>677</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>450</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>399</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>147</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>52</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>1618</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>887</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>9</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>£50-£100</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3">
         <v>4</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>21</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>12</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>29</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>26</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>48</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>67</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>131</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>56</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>19</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>201</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>83</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>£100-£1K</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4">
         <v>13</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>81</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>84</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>94</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>80</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>132</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>233</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>623</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>335</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>210</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>784</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>525</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>12</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>£1K-£5K</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5">
         <v>6</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>54</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>47</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>48</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>38</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>41</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>150</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>254</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>190</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>203</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>319</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>161</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>44</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>14</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>22</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>10</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>13</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>8</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>38</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>50</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>45</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>52</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>56</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>26</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>6</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>£10K-£25K</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>7</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>15</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>6</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>13</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>10</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>38</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>24</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>46</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>30</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>24</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>27</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>5</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>£25K-£50K</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8">
         <v>0</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>5</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>8</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>9</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>3</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>12</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>10</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>13</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>11</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>6</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>10</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>2</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>£50K+</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>1</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>8</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>4</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>2</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>3</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>7</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>5</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>6</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>8</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>10</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>6</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10">
         <v>2</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>6</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>5</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>11</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>8</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>5</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>5</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>5</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>257</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>613</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>672</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10">
         <v>215</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -507,7 +507,7 @@
         <v>508</v>
       </c>
       <c r="F2" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G2" t="n">
         <v>677</v>
@@ -522,7 +522,7 @@
         <v>147</v>
       </c>
       <c r="K2" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L2" t="n">
         <v>1618</v>
@@ -531,7 +531,7 @@
         <v>879</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -577,7 +577,7 @@
         <v>80</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -614,7 +614,7 @@
         <v>335</v>
       </c>
       <c r="K4" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L4" t="n">
         <v>784</v>
@@ -623,7 +623,7 @@
         <v>521</v>
       </c>
       <c r="N4" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -660,16 +660,16 @@
         <v>190</v>
       </c>
       <c r="K5" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L5" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M5" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N5" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -715,7 +715,7 @@
         <v>26</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -731,7 +731,7 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
@@ -869,7 +869,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>11</v>
@@ -890,16 +890,16 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="L10" t="n">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="M10" t="n">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="N10" t="n">
-        <v>245</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,322 +583,414 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>£100-£1K</t>
+          <t>£100-£200</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
+        <v>24</v>
+      </c>
+      <c r="E4" t="n">
+        <v>41</v>
+      </c>
+      <c r="F4" t="n">
+        <v>28</v>
+      </c>
+      <c r="G4" t="n">
+        <v>56</v>
+      </c>
+      <c r="H4" t="n">
+        <v>71</v>
+      </c>
+      <c r="I4" t="n">
+        <v>172</v>
+      </c>
+      <c r="J4" t="n">
         <v>84</v>
       </c>
-      <c r="E4" t="n">
-        <v>94</v>
-      </c>
-      <c r="F4" t="n">
-        <v>80</v>
-      </c>
-      <c r="G4" t="n">
-        <v>132</v>
-      </c>
-      <c r="H4" t="n">
-        <v>233</v>
-      </c>
-      <c r="I4" t="n">
-        <v>623</v>
-      </c>
-      <c r="J4" t="n">
-        <v>335</v>
-      </c>
       <c r="K4" t="n">
-        <v>209</v>
+        <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>784</v>
+        <v>253</v>
       </c>
       <c r="M4" t="n">
-        <v>521</v>
+        <v>151</v>
       </c>
       <c r="N4" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D5" t="n">
+        <v>35</v>
+      </c>
+      <c r="E5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F5" t="n">
+        <v>34</v>
+      </c>
+      <c r="G5" t="n">
         <v>47</v>
       </c>
-      <c r="E5" t="n">
-        <v>48</v>
-      </c>
-      <c r="F5" t="n">
-        <v>38</v>
-      </c>
-      <c r="G5" t="n">
-        <v>41</v>
-      </c>
       <c r="H5" t="n">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="I5" t="n">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="J5" t="n">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="K5" t="n">
-        <v>205</v>
+        <v>101</v>
       </c>
       <c r="L5" t="n">
         <v>318</v>
       </c>
       <c r="M5" t="n">
-        <v>158</v>
+        <v>219</v>
       </c>
       <c r="N5" t="n">
-        <v>52</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="H6" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="I6" t="n">
-        <v>50</v>
+        <v>181</v>
       </c>
       <c r="J6" t="n">
-        <v>45</v>
+        <v>116</v>
       </c>
       <c r="K6" t="n">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="L6" t="n">
-        <v>56</v>
+        <v>213</v>
       </c>
       <c r="M6" t="n">
-        <v>26</v>
+        <v>151</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="H7" t="n">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="I7" t="n">
-        <v>24</v>
+        <v>254</v>
       </c>
       <c r="J7" t="n">
-        <v>46</v>
+        <v>190</v>
       </c>
       <c r="K7" t="n">
-        <v>30</v>
+        <v>205</v>
       </c>
       <c r="L7" t="n">
-        <v>24</v>
+        <v>318</v>
       </c>
       <c r="M7" t="n">
-        <v>27</v>
+        <v>158</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>£25K-£50K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>13</v>
+      </c>
+      <c r="G8" t="n">
         <v>8</v>
       </c>
-      <c r="E8" t="n">
-        <v>9</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
       <c r="H8" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="J8" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="K8" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="M8" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>£50K+</t>
+          <t>£10K-£25K</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="I9" t="n">
+        <v>24</v>
+      </c>
+      <c r="J9" t="n">
+        <v>46</v>
+      </c>
+      <c r="K9" t="n">
+        <v>30</v>
+      </c>
+      <c r="L9" t="n">
+        <v>24</v>
+      </c>
+      <c r="M9" t="n">
+        <v>27</v>
+      </c>
+      <c r="N9" t="n">
         <v>5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L9" t="n">
-        <v>10</v>
-      </c>
-      <c r="M9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>£25K-£50K</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J10" t="n">
+        <v>13</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>£50K+</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>No data</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B12" t="n">
         <v>2</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C12" t="n">
         <v>6</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D12" t="n">
         <v>6</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E12" t="n">
         <v>11</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F12" t="n">
         <v>8</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G12" t="n">
         <v>5</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H12" t="n">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I12" t="n">
         <v>5</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K12" t="n">
         <v>265</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L12" t="n">
         <v>617</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M12" t="n">
         <v>689</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N12" t="n">
         <v>260</v>
       </c>
     </row>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
         <v>6</v>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -531,7 +531,7 @@
         <v>879</v>
       </c>
       <c r="N2" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -577,7 +577,7 @@
         <v>80</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -623,7 +623,7 @@
         <v>151</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -669,7 +669,7 @@
         <v>219</v>
       </c>
       <c r="N5" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
@@ -715,7 +715,7 @@
         <v>151</v>
       </c>
       <c r="N6" t="n">
-        <v>19</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -761,7 +761,7 @@
         <v>158</v>
       </c>
       <c r="N7" t="n">
-        <v>52</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8">
@@ -807,7 +807,7 @@
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -853,7 +853,7 @@
         <v>27</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -899,7 +899,7 @@
         <v>10</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -991,7 +991,7 @@
         <v>689</v>
       </c>
       <c r="N12" t="n">
-        <v>260</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -501,37 +501,37 @@
         <v>247</v>
       </c>
       <c r="D2" t="n">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="E2" t="n">
-        <v>508</v>
+        <v>458</v>
       </c>
       <c r="F2" t="n">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="G2" t="n">
-        <v>677</v>
+        <v>619</v>
       </c>
       <c r="H2" t="n">
-        <v>450</v>
+        <v>356</v>
       </c>
       <c r="I2" t="n">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="J2" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K2" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="L2" t="n">
-        <v>1618</v>
+        <v>1549</v>
       </c>
       <c r="M2" t="n">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="N2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -547,37 +547,37 @@
         <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H3" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="I3" t="n">
         <v>131</v>
       </c>
       <c r="J3" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K3" t="n">
         <v>19</v>
       </c>
       <c r="L3" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M3" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -593,28 +593,28 @@
         <v>19</v>
       </c>
       <c r="D4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E4" t="n">
+        <v>36</v>
+      </c>
+      <c r="F4" t="n">
+        <v>22</v>
+      </c>
+      <c r="G4" t="n">
+        <v>46</v>
+      </c>
+      <c r="H4" t="n">
+        <v>57</v>
+      </c>
+      <c r="I4" t="n">
+        <v>175</v>
+      </c>
+      <c r="J4" t="n">
+        <v>86</v>
+      </c>
+      <c r="K4" t="n">
         <v>24</v>
-      </c>
-      <c r="E4" t="n">
-        <v>41</v>
-      </c>
-      <c r="F4" t="n">
-        <v>28</v>
-      </c>
-      <c r="G4" t="n">
-        <v>56</v>
-      </c>
-      <c r="H4" t="n">
-        <v>71</v>
-      </c>
-      <c r="I4" t="n">
-        <v>172</v>
-      </c>
-      <c r="J4" t="n">
-        <v>84</v>
-      </c>
-      <c r="K4" t="n">
-        <v>25</v>
       </c>
       <c r="L4" t="n">
         <v>253</v>
@@ -623,7 +623,7 @@
         <v>151</v>
       </c>
       <c r="N4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -639,37 +639,37 @@
         <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H5" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I5" t="n">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="J5" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="K5" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L5" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M5" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="N5" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -685,37 +685,37 @@
         <v>22</v>
       </c>
       <c r="D6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E6" t="n">
         <v>25</v>
       </c>
-      <c r="E6" t="n">
-        <v>30</v>
-      </c>
       <c r="F6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H6" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="I6" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="J6" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="K6" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L6" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M6" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="N6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -731,37 +731,37 @@
         <v>54</v>
       </c>
       <c r="D7" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="H7" t="n">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="I7" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J7" t="n">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="K7" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L7" t="n">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="M7" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="N7" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8">
@@ -774,34 +774,34 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="n">
         <v>10</v>
-      </c>
-      <c r="F8" t="n">
-        <v>13</v>
       </c>
       <c r="G8" t="n">
         <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J8" t="n">
         <v>45</v>
       </c>
       <c r="K8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L8" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
@@ -823,19 +823,19 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I9" t="n">
         <v>24</v>
@@ -844,10 +844,10 @@
         <v>46</v>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L9" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M9" t="n">
         <v>27</v>
@@ -875,22 +875,22 @@
         <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
         <v>6</v>
@@ -915,22 +915,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
         <v>6</v>
@@ -945,7 +945,7 @@
         <v>6</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -961,13 +961,13 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
         <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
         <v>5</v>
@@ -979,19 +979,19 @@
         <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>265</v>
+        <v>24</v>
       </c>
       <c r="L12" t="n">
-        <v>617</v>
+        <v>74</v>
       </c>
       <c r="M12" t="n">
-        <v>689</v>
+        <v>653</v>
       </c>
       <c r="N12" t="n">
-        <v>353</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -623,7 +623,7 @@
         <v>151</v>
       </c>
       <c r="N4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -991,7 +991,7 @@
         <v>653</v>
       </c>
       <c r="N12" t="n">
-        <v>300</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -991,7 +991,7 @@
         <v>653</v>
       </c>
       <c r="N12" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -991,7 +991,7 @@
         <v>653</v>
       </c>
       <c r="N12" t="n">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -1,40 +1,126 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+  <si>
+    <t>GMV slab</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>£0-£50</t>
+  </si>
+  <si>
+    <t>£50-£100</t>
+  </si>
+  <si>
+    <t>£100-£200</t>
+  </si>
+  <si>
+    <t>£200-£500</t>
+  </si>
+  <si>
+    <t>£500-£1K</t>
+  </si>
+  <si>
+    <t>£1K-£5K</t>
+  </si>
+  <si>
+    <t>£5K-£10K</t>
+  </si>
+  <si>
+    <t>£10K-£25K</t>
+  </si>
+  <si>
+    <t>£25K-£50K</t>
+  </si>
+  <si>
+    <t>£50K+</t>
+  </si>
+  <si>
+    <t>No data</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +128,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,593 +445,539 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>GMV slab</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="n">
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>12</v>
+      </c>
+      <c r="C2">
         <v>247</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>397</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>458</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>293</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>619</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>356</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>393</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>151</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>37</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>1549</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>887</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>26</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>£50-£100</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3">
         <v>4</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>21</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>11</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>21</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>18</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>37</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>51</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>131</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>58</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>19</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>199</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>81</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>8</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>£100-£200</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>19</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>21</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>36</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>22</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>46</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>57</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>175</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>86</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>24</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>253</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>151</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>31</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>£200-£500</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5">
         <v>7</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>40</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>30</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>16</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>27</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>39</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>84</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>264</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>141</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>102</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>320</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>225</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>48</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6">
         <v>3</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>22</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>21</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>25</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>14</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>22</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>59</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>176</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>120</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>86</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>215</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>154</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>59</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>£1K-£5K</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>54</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>40</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>37</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>26</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>28</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>128</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>252</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>206</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>208</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>331</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>161</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>114</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>£5K-£10K</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>13</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>21</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>7</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>10</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>8</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>32</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>53</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>45</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>53</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>60</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>26</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>15</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>£10K-£25K</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>7</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>11</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>5</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>11</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>8</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>35</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>24</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>46</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>31</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>27</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>27</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>8</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>£25K-£50K</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10">
         <v>0</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>5</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>8</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>9</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>1</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>1</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>11</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>10</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>15</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>12</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>6</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>10</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10">
         <v>3</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>£50K+</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>1</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>5</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>5</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>2</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>7</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>6</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>6</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>8</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>10</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>6</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11">
         <v>2</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>6</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>5</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>11</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>7</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>5</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>2</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>5</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>4</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>24</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>74</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>653</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12">
         <v>323</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -531,7 +531,7 @@
         <v>887</v>
       </c>
       <c r="N2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -577,7 +577,7 @@
         <v>81</v>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -623,7 +623,7 @@
         <v>151</v>
       </c>
       <c r="N4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -669,7 +669,7 @@
         <v>225</v>
       </c>
       <c r="N5" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -761,7 +761,7 @@
         <v>161</v>
       </c>
       <c r="N7" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8">
@@ -853,7 +853,7 @@
         <v>27</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -991,7 +991,7 @@
         <v>653</v>
       </c>
       <c r="N12" t="n">
-        <v>333</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -761,7 +761,7 @@
         <v>161</v>
       </c>
       <c r="N7" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8">
@@ -991,7 +991,7 @@
         <v>653</v>
       </c>
       <c r="N12" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -531,7 +531,7 @@
         <v>887</v>
       </c>
       <c r="N2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -623,7 +623,7 @@
         <v>151</v>
       </c>
       <c r="N4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -669,7 +669,7 @@
         <v>225</v>
       </c>
       <c r="N5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
@@ -709,7 +709,7 @@
         <v>86</v>
       </c>
       <c r="L6" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M6" t="n">
         <v>154</v>
@@ -746,7 +746,7 @@
         <v>128</v>
       </c>
       <c r="I7" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J7" t="n">
         <v>206</v>
@@ -755,13 +755,13 @@
         <v>208</v>
       </c>
       <c r="L7" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M7" t="n">
         <v>161</v>
       </c>
       <c r="N7" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8">
@@ -792,7 +792,7 @@
         <v>32</v>
       </c>
       <c r="I8" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J8" t="n">
         <v>45</v>
@@ -807,7 +807,7 @@
         <v>26</v>
       </c>
       <c r="N8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -991,7 +991,7 @@
         <v>653</v>
       </c>
       <c r="N12" t="n">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -516,7 +516,7 @@
         <v>356</v>
       </c>
       <c r="I2" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J2" t="n">
         <v>151</v>
@@ -525,13 +525,13 @@
         <v>37</v>
       </c>
       <c r="L2" t="n">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="M2" t="n">
         <v>887</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -544,7 +544,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
@@ -571,13 +571,13 @@
         <v>19</v>
       </c>
       <c r="L3" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M3" t="n">
         <v>81</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -590,7 +590,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
         <v>21</v>
@@ -608,7 +608,7 @@
         <v>57</v>
       </c>
       <c r="I4" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J4" t="n">
         <v>86</v>
@@ -617,13 +617,13 @@
         <v>24</v>
       </c>
       <c r="L4" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="M4" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -636,10 +636,10 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" t="n">
         <v>16</v>
@@ -663,13 +663,13 @@
         <v>102</v>
       </c>
       <c r="L5" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M5" t="n">
         <v>225</v>
       </c>
       <c r="N5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +685,10 @@
         <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" t="n">
         <v>14</v>
@@ -703,19 +703,19 @@
         <v>176</v>
       </c>
       <c r="J6" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K6" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L6" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M6" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="N6" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -728,13 +728,13 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D7" t="n">
         <v>40</v>
       </c>
       <c r="E7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7" t="n">
         <v>26</v>
@@ -746,22 +746,22 @@
         <v>128</v>
       </c>
       <c r="I7" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J7" t="n">
+        <v>207</v>
+      </c>
+      <c r="K7" t="n">
         <v>206</v>
-      </c>
-      <c r="K7" t="n">
-        <v>208</v>
       </c>
       <c r="L7" t="n">
         <v>332</v>
       </c>
       <c r="M7" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N7" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8">
@@ -792,7 +792,7 @@
         <v>32</v>
       </c>
       <c r="I8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J8" t="n">
         <v>45</v>
@@ -801,7 +801,7 @@
         <v>53</v>
       </c>
       <c r="L8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M8" t="n">
         <v>26</v>
@@ -884,7 +884,7 @@
         <v>11</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
         <v>15</v>
@@ -893,7 +893,7 @@
         <v>12</v>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
         <v>10</v>
@@ -930,7 +930,7 @@
         <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
         <v>6</v>
@@ -991,7 +991,7 @@
         <v>653</v>
       </c>
       <c r="N12" t="n">
-        <v>355</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -715,7 +715,7 @@
         <v>152</v>
       </c>
       <c r="N6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
@@ -991,7 +991,7 @@
         <v>653</v>
       </c>
       <c r="N12" t="n">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -498,7 +498,7 @@
         <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D2" t="n">
         <v>397</v>
@@ -507,7 +507,7 @@
         <v>458</v>
       </c>
       <c r="F2" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G2" t="n">
         <v>619</v>
@@ -519,19 +519,19 @@
         <v>394</v>
       </c>
       <c r="J2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L2" t="n">
-        <v>1551</v>
+        <v>1556</v>
       </c>
       <c r="M2" t="n">
-        <v>887</v>
+        <v>966</v>
       </c>
       <c r="N2" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -568,16 +568,16 @@
         <v>58</v>
       </c>
       <c r="K3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3" t="n">
         <v>198</v>
       </c>
       <c r="M3" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -617,13 +617,13 @@
         <v>24</v>
       </c>
       <c r="L4" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M4" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="N4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
@@ -660,16 +660,16 @@
         <v>141</v>
       </c>
       <c r="K5" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L5" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M5" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="N5" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
@@ -706,16 +706,16 @@
         <v>119</v>
       </c>
       <c r="K6" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L6" t="n">
         <v>213</v>
       </c>
       <c r="M6" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="N6" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
@@ -752,16 +752,16 @@
         <v>207</v>
       </c>
       <c r="K7" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L7" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M7" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="N7" t="n">
-        <v>135</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8">
@@ -804,10 +804,10 @@
         <v>59</v>
       </c>
       <c r="M8" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="N8" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -850,10 +850,10 @@
         <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -958,7 +958,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
         <v>5</v>
@@ -967,7 +967,7 @@
         <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
         <v>5</v>
@@ -979,19 +979,19 @@
         <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="L12" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="M12" t="n">
-        <v>653</v>
+        <v>537</v>
       </c>
       <c r="N12" t="n">
-        <v>374</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -531,7 +531,7 @@
         <v>966</v>
       </c>
       <c r="N2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
@@ -669,7 +669,7 @@
         <v>233</v>
       </c>
       <c r="N5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6">
@@ -991,7 +991,7 @@
         <v>537</v>
       </c>
       <c r="N12" t="n">
-        <v>257</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -991,7 +991,7 @@
         <v>537</v>
       </c>
       <c r="N12" t="n">
-        <v>325</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -531,7 +531,7 @@
         <v>966</v>
       </c>
       <c r="N2" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
@@ -577,7 +577,7 @@
         <v>84</v>
       </c>
       <c r="N3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -617,13 +617,13 @@
         <v>24</v>
       </c>
       <c r="L4" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="M4" t="n">
         <v>157</v>
       </c>
       <c r="N4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
@@ -669,7 +669,7 @@
         <v>233</v>
       </c>
       <c r="N5" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6">
@@ -703,7 +703,7 @@
         <v>176</v>
       </c>
       <c r="J6" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K6" t="n">
         <v>89</v>
@@ -715,7 +715,7 @@
         <v>160</v>
       </c>
       <c r="N6" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7">
@@ -749,19 +749,19 @@
         <v>252</v>
       </c>
       <c r="J7" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K7" t="n">
         <v>208</v>
       </c>
       <c r="L7" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M7" t="n">
         <v>171</v>
       </c>
       <c r="N7" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8">
@@ -807,7 +807,7 @@
         <v>29</v>
       </c>
       <c r="N8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -853,7 +853,7 @@
         <v>28</v>
       </c>
       <c r="N9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -945,7 +945,7 @@
         <v>6</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -991,7 +991,7 @@
         <v>537</v>
       </c>
       <c r="N12" t="n">
-        <v>335</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -991,7 +991,7 @@
         <v>537</v>
       </c>
       <c r="N12" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -528,10 +528,10 @@
         <v>1556</v>
       </c>
       <c r="M2" t="n">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="N2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -568,13 +568,13 @@
         <v>58</v>
       </c>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L3" t="n">
         <v>198</v>
       </c>
       <c r="M3" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N3" t="n">
         <v>16</v>
@@ -614,16 +614,16 @@
         <v>86</v>
       </c>
       <c r="K4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="M4" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="N4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
@@ -645,7 +645,7 @@
         <v>16</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
         <v>39</v>
@@ -660,16 +660,16 @@
         <v>141</v>
       </c>
       <c r="K5" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L5" t="n">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="M5" t="n">
         <v>233</v>
       </c>
       <c r="N5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
@@ -706,16 +706,16 @@
         <v>120</v>
       </c>
       <c r="K6" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L6" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M6" t="n">
         <v>160</v>
       </c>
       <c r="N6" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
@@ -737,7 +737,7 @@
         <v>36</v>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G7" t="n">
         <v>28</v>
@@ -749,19 +749,19 @@
         <v>252</v>
       </c>
       <c r="J7" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K7" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L7" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="M7" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N7" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8">
@@ -795,19 +795,19 @@
         <v>53</v>
       </c>
       <c r="J8" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K8" t="n">
         <v>53</v>
       </c>
       <c r="L8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N8" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
@@ -841,19 +841,19 @@
         <v>24</v>
       </c>
       <c r="J9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K9" t="n">
         <v>31</v>
       </c>
       <c r="L9" t="n">
+        <v>28</v>
+      </c>
+      <c r="M9" t="n">
         <v>27</v>
       </c>
-      <c r="M9" t="n">
-        <v>28</v>
-      </c>
       <c r="N9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -887,7 +887,7 @@
         <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" t="n">
         <v>12</v>
@@ -899,7 +899,7 @@
         <v>10</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -988,10 +988,10 @@
         <v>64</v>
       </c>
       <c r="M12" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N12" t="n">
-        <v>315</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -543,13 +543,13 @@
         <v>40</v>
       </c>
       <c r="M2">
-        <v>1553</v>
+        <v>1556</v>
       </c>
       <c r="N2">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="O2">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="P2">
         <v>44</v>
@@ -593,7 +593,7 @@
         <v>20</v>
       </c>
       <c r="M3">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N3">
         <v>83</v>
@@ -643,10 +643,10 @@
         <v>24</v>
       </c>
       <c r="M4">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N4">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O4">
         <v>44</v>
@@ -746,7 +746,7 @@
         <v>214</v>
       </c>
       <c r="N6">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O6">
         <v>87</v>
@@ -796,7 +796,7 @@
         <v>331</v>
       </c>
       <c r="N7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O7">
         <v>183</v>
@@ -1043,13 +1043,13 @@
         <v>15</v>
       </c>
       <c r="M12">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="N12">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="O12">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="P12">
         <v>29</v>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -911,7 +911,7 @@
         <v>17</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1067,7 +1067,7 @@
         <v>292</v>
       </c>
       <c r="P12" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -547,7 +547,7 @@
         <v>85</v>
       </c>
       <c r="P2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -752,10 +752,10 @@
         <v>154</v>
       </c>
       <c r="O6" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -1064,10 +1064,10 @@
         <v>527</v>
       </c>
       <c r="O12" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -541,7 +541,7 @@
         <v>1556</v>
       </c>
       <c r="N2" t="n">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="O2" t="n">
         <v>85</v>
@@ -596,7 +596,7 @@
         <v>83</v>
       </c>
       <c r="O3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -648,7 +648,7 @@
         <v>161</v>
       </c>
       <c r="O4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P4" t="n">
         <v>7</v>
@@ -697,7 +697,7 @@
         <v>320</v>
       </c>
       <c r="N5" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="O5" t="n">
         <v>81</v>
@@ -749,7 +749,7 @@
         <v>214</v>
       </c>
       <c r="N6" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O6" t="n">
         <v>86</v>
@@ -905,7 +905,7 @@
         <v>26</v>
       </c>
       <c r="N9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O9" t="n">
         <v>17</v>
@@ -1061,13 +1061,13 @@
         <v>62</v>
       </c>
       <c r="N12" t="n">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="O12" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -1015,7 +1015,7 @@
         <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1067,7 +1067,7 @@
         <v>292</v>
       </c>
       <c r="P12" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -541,13 +541,13 @@
         <v>1556</v>
       </c>
       <c r="N2" t="n">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="O2" t="n">
         <v>86</v>
       </c>
       <c r="P2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -1061,13 +1061,13 @@
         <v>62</v>
       </c>
       <c r="N12" t="n">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O12" t="n">
         <v>292</v>
       </c>
       <c r="P12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/slab_mix_by_month.xlsx
+++ b/slab_mix_by_month.xlsx
@@ -1067,7 +1067,7 @@
         <v>292</v>
       </c>
       <c r="P12" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
